--- a/artfynd/A 34832-2025 artfynd.xlsx
+++ b/artfynd/A 34832-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414883</v>
       </c>
       <c r="B2" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414879</v>
       </c>
       <c r="B3" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34832-2025 artfynd.xlsx
+++ b/artfynd/A 34832-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414883</v>
       </c>
       <c r="B2" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414879</v>
       </c>
       <c r="B3" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34832-2025 artfynd.xlsx
+++ b/artfynd/A 34832-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414883</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414879</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34832-2025 artfynd.xlsx
+++ b/artfynd/A 34832-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414883</v>
       </c>
       <c r="B2" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414879</v>
       </c>
       <c r="B3" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34832-2025 artfynd.xlsx
+++ b/artfynd/A 34832-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414883</v>
       </c>
       <c r="B2" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414879</v>
       </c>
       <c r="B3" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34832-2025 artfynd.xlsx
+++ b/artfynd/A 34832-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414883</v>
       </c>
       <c r="B2" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414879</v>
       </c>
       <c r="B3" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34832-2025 artfynd.xlsx
+++ b/artfynd/A 34832-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414883</v>
       </c>
       <c r="B2" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414879</v>
       </c>
       <c r="B3" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34832-2025 artfynd.xlsx
+++ b/artfynd/A 34832-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414883</v>
       </c>
       <c r="B2" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414879</v>
       </c>
       <c r="B3" t="n">
-        <v>98385</v>
+        <v>98386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34832-2025 artfynd.xlsx
+++ b/artfynd/A 34832-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414883</v>
       </c>
       <c r="B2" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414879</v>
       </c>
       <c r="B3" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34832-2025 artfynd.xlsx
+++ b/artfynd/A 34832-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>130314228</v>
       </c>
       <c r="B4" t="n">
-        <v>57007</v>
+        <v>57033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34832-2025 artfynd.xlsx
+++ b/artfynd/A 34832-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>130314228</v>
       </c>
       <c r="B4" t="n">
-        <v>57033</v>
+        <v>57035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34832-2025 artfynd.xlsx
+++ b/artfynd/A 34832-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>130314228</v>
       </c>
       <c r="B4" t="n">
-        <v>57035</v>
+        <v>57043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34832-2025 artfynd.xlsx
+++ b/artfynd/A 34832-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>130314228</v>
       </c>
       <c r="B4" t="n">
-        <v>57043</v>
+        <v>57044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
